--- a/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
+++ b/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
@@ -10,11 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Scope" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer A" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer B" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer C" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optional Items" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer B1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer B2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offer C" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optional Items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,7 +597,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>A 300만–800만원 (초기 300만–500만원) · B 디자인 파트너 1,000만–1,500만원 · B 표준 1,500만–2,500만원 · C 월 300만–600만원</t>
+          <t>A 진단 워크숍 초기형 300만–500만원 · A 확장형 500만–800만원 · B1 디자인 파트너 1,000만–1,500만원 · B2 표준 1,500만–2,500만원 · C 운영 자문 월 300만–600만원</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>표준 300만–800만원 / 초기 300만–500만원</t>
+          <t>초기형 300만–500만원 / 확장형 500만–800만원</t>
         </is>
       </c>
     </row>
@@ -945,14 +946,14 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>B · 6주 디자인 파트너 파일럿</t>
+          <t>B1 · 6주 디자인 파트너 파일럿</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>디자인 파트너 1,000만–1,500만원</t>
+          <t>1,000만–1,500만원</t>
         </is>
       </c>
     </row>
@@ -1094,6 +1095,155 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
+          <t>B2 · 6주 표준 파일럿</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>1,500만–2,500만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>금액(원, VAT 별도)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>기본 견적</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>공급가액</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>VAT (10%)</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>ROUND(B5*0.1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>합계 (VAT 포함)</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>B5+B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>지급 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>착수금 50%</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>ROUND(B5*0.5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>최종 산출물 검수 후 잔금 50%</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>ROUND(B5*0.5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>참고: 견적 검토 템플릿 — 계약 확정 문서 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>표준 범위: 15,000,000 – 25,000,000 원 (VAT 별도). 범위 밖 값은 빨간 경고 표시.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(B4&lt;15000000,B4&gt;25000000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
           <t>C · 조직 운영 자문 (월)</t>
         </is>
       </c>
@@ -1225,7 +1375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1311,7 +1461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1420,7 +1570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
+++ b/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
@@ -100,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -122,24 +122,58 @@
         <color rgb="00B0B7C0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B7C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B7C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B7C0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B7C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B7C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B7C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -536,7 +570,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>CUSTOMER-FACING MASTER · FINAL IDENTITY REQUIRED · LEGAL REVIEW REQUIRED · NOT YET SENT</t>
+          <t>공급자: 파디엠</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
@@ -544,98 +578,118 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>제안 제공자 정보는 발송 전 최종 확정</t>
+          <t>제공 및 계약 주체: 파디엠</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>견적 발행 주체: 파디엠</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>사용 방법</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>각 Offer sheet에 금액(원, VAT 별도)과 인원·기간을 입력합니다.</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>계산</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>공급가액 / VAT(10%) / 합계가 자동 계산됩니다. 지급 단계(착수금 50%·잔금 50%)를 확인합니다.</t>
+          <t>사용 방법</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>각 Offer sheet에 금액(원, VAT 별도)과 인원·기간을 입력합니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>경고</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>표준 가격 범위를 벗어나는 금액을 입력하면 해당 셀에 경고가 표시됩니다.</t>
+          <t>계산</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>공급가액 / VAT(10%) / 합계가 자동 계산됩니다. 지급 단계(착수금 50%·잔금 50%)를 확인합니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>표준 가격</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>A 진단 워크숍 초기형 300만–500만원 · A 확장형 500만–800만원 · B1 디자인 파트너 1,000만–1,500만원 · B2 표준 1,500만–2,500만원 · C 운영 자문 월 300만–600만원</t>
+          <t>경고</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>표준 가격 범위를 벗어나는 금액을 입력하면 해당 셀에 경고가 표시됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>견적 검토 템플릿 — 계약 확정 문서가 아닙니다.</t>
+          <t>표준 가격</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>A 진단 워크숍 초기형 300만–500만원 · A 확장형 500만–800만원 · B1 디자인 파트너 1,000만–1,500만원 · B2 표준 1,500만–2,500만원 · C 운영 자문 월 300만–600만원</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>견적 검토 템플릿 — 계약 확정 문서가 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>가격 정책</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>시장 검증 전 자사 가격 가설 · 범위와 인원·기간에 따라 최종 견적 · VAT 조건은 최종 견적서에서 확정</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>발송 전 공식 사업자 정보 입력 필요 (사업자등록번호·대표자·주소·연락처·계좌).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>본 템플릿은 고객에게 발송 전 최종 승인과 전문 법률·계약 검토가 필요합니다.</t>
         </is>
@@ -1576,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1593,76 +1647,147 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>견적 준비자</t>
+          <t>제공 및 계약 주체</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>[이름/직책]</t>
+          <t>파디엠</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>견적 승인자 (제공자)</t>
+          <t>공급자</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>[이름/직책]</t>
+          <t>파디엠</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>고객 승인자</t>
+          <t>사업자등록번호</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>[직책]</t>
+          <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>승인일</t>
+          <t>대표자·주소·연락처</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>[YYYY-MM-DD]</t>
+          <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>입금 계좌 (은행명·예금주)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>견적 검토 중 (계약 확정 아님)</t>
+          <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>견적 준비자</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>[이름/직책]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>견적 승인자 (제공자)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>[이름/직책]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>고객 승인자</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>[직책]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>승인일</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>[YYYY-MM-DD]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>견적 검토 중 (계약 확정 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>법률·계약 검토</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>REQUIRED — DRAFT · PROFESSIONAL LEGAL REVIEW REQUIRED</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>안내: 사업자등록번호·대표자·주소·연락처·계좌 정보는 발송 전 공식 확인 후 입력합니다.</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:B15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
+++ b/docs/commercial/business-35-ai-media-education-dx/customer-package/Business35_Pilot_Quote_Template.xlsx
@@ -159,20 +159,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +658,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>표준 가격</t>
@@ -639,7 +666,8 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>A 진단 워크숍 초기형 300만–500만원 · A 확장형 500만–800만원 · B1 디자인 파트너 1,000만–1,500만원 · B2 표준 1,500만–2,500만원 · C 운영 자문 월 300만–600만원</t>
+          <t>A 초기형 300만–500만원 · A 확장형 500만–800만원
+B1 1,000만–1,500만원 · B2 1,500만–2,500만원 · C 월 300만–600만원</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1569,7 @@
           <t>범위</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>1팀·1핵심 업무 · 6주 파일럿 (Week 0–6)</t>
         </is>
@@ -1553,7 +1581,7 @@
           <t>참여</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>팀 주당 2–4시간 · 운영 책임자 1인 지정</t>
         </is>
@@ -1565,7 +1593,7 @@
           <t>산출물</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>기준선 진단 · 교육 · 워크플로 재설계 · 성과·위험 보고 · 운영 플레이북</t>
         </is>
@@ -1577,7 +1605,7 @@
           <t>제외</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>전사 확산 · 시스템 구축 · AI 도구 라이선스 구매 · 법률 자문</t>
         </is>
@@ -1589,7 +1617,7 @@
           <t>데이터</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>개인정보 원문은 외부 AI 입력 금지 · 입력 금지 자료 준수</t>
         </is>
@@ -1601,7 +1629,7 @@
           <t>가격</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>시장 검증 전 자사 가격 가설 · 실제 견적은 범위 확인 후 별도 승인</t>
         </is>
@@ -1613,7 +1641,7 @@
           <t>VAT</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>VAT 조건은 최종 견적서에서 확정</t>
         </is>
@@ -1650,7 +1678,7 @@
           <t>제공 및 계약 주체</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>파디엠</t>
         </is>
@@ -1662,7 +1690,7 @@
           <t>공급자</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>파디엠</t>
         </is>
@@ -1674,7 +1702,7 @@
           <t>사업자등록번호</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
@@ -1686,7 +1714,7 @@
           <t>대표자·주소·연락처</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
@@ -1698,7 +1726,7 @@
           <t>입금 계좌 (은행명·예금주)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>발송 전 공식 사업자 정보 입력 필요</t>
         </is>
@@ -1710,7 +1738,7 @@
           <t>견적 준비자</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>[이름/직책]</t>
         </is>
@@ -1722,7 +1750,7 @@
           <t>견적 승인자 (제공자)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>[이름/직책]</t>
         </is>
@@ -1734,7 +1762,7 @@
           <t>고객 승인자</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>[직책]</t>
         </is>
@@ -1746,7 +1774,7 @@
           <t>승인일</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>[YYYY-MM-DD]</t>
         </is>
@@ -1758,21 +1786,21 @@
           <t>상태</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>견적 검토 중 (계약 확정 아님)</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>법률·계약 검토</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>REQUIRED — DRAFT · PROFESSIONAL LEGAL REVIEW REQUIRED</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>전문 법률·계약 검토 필요 — 최종 발송 전 확인</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1810,7 @@
           <t>안내: 사업자등록번호·대표자·주소·연락처·계좌 정보는 발송 전 공식 확인 후 입력합니다.</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n"/>
+      <c r="B15" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
